--- a/output/pdf_financials_xlsx/AAUC.xlsx
+++ b/output/pdf_financials_xlsx/AAUC.xlsx
@@ -2488,19 +2488,19 @@
         </is>
       </c>
       <c r="B92" s="3" t="n">
-        <v>0</v>
+        <v>0.000437</v>
       </c>
       <c r="C92" s="3" t="n">
-        <v>0</v>
+        <v>29.506</v>
       </c>
       <c r="D92" s="3" t="n">
-        <v>0</v>
+        <v>2.419</v>
       </c>
       <c r="E92" s="3" t="n">
-        <v>0</v>
+        <v>8.492000000000001</v>
       </c>
       <c r="F92" s="3" t="n">
-        <v>0</v>
+        <v>30.914</v>
       </c>
     </row>
     <row r="93">
@@ -3048,10 +3048,10 @@
         <v>0</v>
       </c>
       <c r="C118" s="3" t="n">
-        <v>0</v>
+        <v>-26.386</v>
       </c>
       <c r="D118" s="3" t="n">
-        <v>0</v>
+        <v>-23.404</v>
       </c>
       <c r="E118" s="3" t="n">
         <v>0</v>
@@ -4882,7 +4882,11 @@
           <t>Share-based payments reserve 28</t>
         </is>
       </c>
-      <c r="D35" t="inlineStr"/>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E35" t="inlineStr">
         <is>
           <t>-</t>
@@ -6197,7 +6201,11 @@
           <t>Share-based payments reserve 29</t>
         </is>
       </c>
-      <c r="D68" t="inlineStr"/>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E68" t="inlineStr">
         <is>
           <t>-</t>
@@ -6533,7 +6541,11 @@
           <t>Reserves (Note 6)</t>
         </is>
       </c>
-      <c r="D76" t="inlineStr"/>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E76" s="5" t="n">
         <v>0.000437</v>
       </c>
@@ -9789,7 +9801,11 @@
           <t>Exploration and evaluation expenditure</t>
         </is>
       </c>
-      <c r="D158" t="inlineStr"/>
+      <c r="D158" t="inlineStr">
+        <is>
+          <t>NetOtherInvestingChanges</t>
+        </is>
+      </c>
       <c r="E158" t="inlineStr">
         <is>
           <t>-</t>

--- a/output/pdf_financials_xlsx/AAUC.xlsx
+++ b/output/pdf_financials_xlsx/AAUC.xlsx
@@ -1188,7 +1188,7 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>0.018339</v>
       </c>
       <c r="C34" s="3" t="n">
         <v>45.163</v>
@@ -1232,7 +1232,7 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0</v>
+        <v>0.018339</v>
       </c>
       <c r="C36" s="3" t="n">
         <v>45.163</v>
@@ -6285,7 +6285,7 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E70" s="5" t="n">

--- a/output/pdf_financials_xlsx/AAUC.xlsx
+++ b/output/pdf_financials_xlsx/AAUC.xlsx
@@ -656,10 +656,10 @@
         <v>106.79</v>
       </c>
       <c r="E11" s="3" t="n">
-        <v>220.234</v>
+        <v>13.91</v>
       </c>
       <c r="F11" s="3" t="n">
-        <v>506.542</v>
+        <v>263.903</v>
       </c>
     </row>
     <row r="12">
@@ -11631,7 +11631,11 @@
           <t>Net earnings before finance costs and income tax $</t>
         </is>
       </c>
-      <c r="D202" t="inlineStr"/>
+      <c r="D202" t="inlineStr">
+        <is>
+          <t>OperatingIncome</t>
+        </is>
+      </c>
       <c r="E202" t="inlineStr">
         <is>
           <t>-</t>
